--- a/trading_journal_v4.xlsx
+++ b/trading_journal_v4.xlsx
@@ -885,7 +885,9 @@
         <v>68.11</v>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>1.66</v>
+      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -1005,7 +1007,9 @@
         <v>52.47</v>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0.61</v>
+      </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>

--- a/trading_journal_v4.xlsx
+++ b/trading_journal_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>44.64</v>
+        <v>44.6</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>16.86</v>
+        <v>16.8</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>50.53</v>
+        <v>48.93</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>223.7</v>
+        <v>211.81</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>232.01</v>
+        <v>228.23</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11.49</v>
+        <v>11.52</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>40.15</v>
+        <v>39.07</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>33.7</v>
+        <v>33.35</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>249.96</v>
+        <v>250.45</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -882,14 +882,14 @@
         <v>68.11</v>
       </c>
       <c r="I11" t="n">
-        <v>68.11</v>
+        <v>68.05</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="12">
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>75.44</v>
+        <v>76.36</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>111.71</v>
+        <v>113.9</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1004,13 +1004,333 @@
         <v>52.47</v>
       </c>
       <c r="I14" t="n">
-        <v>52.47</v>
+        <v>51.55</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>0.61</v>
+        <v>-1.15</v>
       </c>
       <c r="L14" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="D15" t="n">
+        <v>140.11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-457.07</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>147.96</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="E16" t="n">
+        <v>141.06</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="D17" t="n">
+        <v>262.11</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1598.97</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>268.53</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LFST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1980.29</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NOG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>382.71</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1919.01</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>257.81</v>
+      </c>
+      <c r="D20" t="n">
+        <v>254.19</v>
+      </c>
+      <c r="E20" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>262.72</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>200.54</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1114.94</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>219.41</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IOT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>67</v>
+      </c>
+      <c r="D22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E22" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
         <v>0</v>
       </c>
     </row>

--- a/trading_journal_v4.xlsx
+++ b/trading_journal_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>44.6</v>
+        <v>44.23</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>16.8</v>
+        <v>16.97</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>48.93</v>
+        <v>49.79</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>211.81</v>
+        <v>211.79</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>228.23</v>
+        <v>229.2</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11.52</v>
+        <v>11.57</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>39.07</v>
+        <v>39.56</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>33.35</v>
+        <v>33.45</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>250.45</v>
+        <v>250.09</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -882,14 +882,14 @@
         <v>68.11</v>
       </c>
       <c r="I11" t="n">
-        <v>68.05</v>
+        <v>68.13</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="12">
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>76.36</v>
+        <v>74.91</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>113.9</v>
+        <v>115.28</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1004,14 +1004,14 @@
         <v>52.47</v>
       </c>
       <c r="I14" t="n">
-        <v>51.55</v>
+        <v>51.45</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>-1.15</v>
+        <v>-1.34</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.92</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="15">
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>147.96</v>
+        <v>149.06</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>24.13</v>
+        <v>24.46</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>268.53</v>
+        <v>273.76</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>13.1</v>
+        <v>13.39</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>28.15</v>
+        <v>28.09</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>262.72</v>
+        <v>260.98</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>219.41</v>
+        <v>220.12</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1326,11 +1326,251 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>43.51</v>
+        <v>43.01</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HMC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="D23" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="E23" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="I23" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CNQ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="D24" t="n">
+        <v>51.37</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3240.09</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CVI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="D25" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KNTK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>243.98</v>
+      </c>
+      <c r="D26" t="n">
+        <v>52.76</v>
+      </c>
+      <c r="E26" t="n">
+        <v>817.64</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ATRC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-148</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>61.42</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="D28" t="n">
+        <v>116.79</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-83.95999999999999</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>130.03</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/trading_journal_v4.xlsx
+++ b/trading_journal_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>44.23</v>
+        <v>44.27</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>16.97</v>
+        <v>16.88</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>49.79</v>
+        <v>50.35</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>211.79</v>
+        <v>212.16</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>229.2</v>
+        <v>231.46</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11.57</v>
+        <v>11.31</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>39.56</v>
+        <v>39.58</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>33.45</v>
+        <v>32.74</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>250.09</v>
+        <v>259.86</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -882,14 +882,14 @@
         <v>68.11</v>
       </c>
       <c r="I11" t="n">
-        <v>68.13</v>
+        <v>71.8</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>1.69</v>
+        <v>7.16</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="12">
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>74.91</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>115.28</v>
+        <v>116.9</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1004,14 +1004,14 @@
         <v>52.47</v>
       </c>
       <c r="I14" t="n">
-        <v>51.45</v>
+        <v>52.55</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>-1.34</v>
+        <v>0.77</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.02</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="15">
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>149.06</v>
+        <v>150.03</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>24.46</v>
+        <v>25.08</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>273.76</v>
+        <v>273.61</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>13.39</v>
+        <v>13.64</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>28.09</v>
+        <v>27.81</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>260.98</v>
+        <v>263.45</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>220.12</v>
+        <v>204.1</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>43.01</v>
+        <v>41.65</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1366,12 +1366,14 @@
         <v>67.36</v>
       </c>
       <c r="I23" t="n">
-        <v>33.68</v>
+        <v>33.89</v>
       </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>2.51</v>
+      </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="24">
@@ -1406,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>54.81</v>
+        <v>55.09</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1446,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>57.07</v>
+        <v>56.82</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1486,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>56.61</v>
+        <v>58.09</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1526,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>61.42</v>
+        <v>62.48</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1566,11 +1568,171 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>130.03</v>
+        <v>131.18</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FANG</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>205</v>
+      </c>
+      <c r="D29" t="n">
+        <v>195.38</v>
+      </c>
+      <c r="E29" t="n">
+        <v>233.86</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>206.43</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HPK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E30" t="n">
+        <v>215.39</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FET</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="D31" t="n">
+        <v>81.63</v>
+      </c>
+      <c r="E31" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>88.76000000000001</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="D32" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="E32" t="n">
+        <v>291.29</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
         <v>0</v>
       </c>
     </row>

--- a/trading_journal_v4.xlsx
+++ b/trading_journal_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>44.27</v>
+        <v>43.37</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>50.35</v>
+        <v>50.39</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>212.16</v>
+        <v>206.14</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>231.46</v>
+        <v>235.52</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11.31</v>
+        <v>11.33</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>39.58</v>
+        <v>40.38</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>32.74</v>
+        <v>31.17</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>259.86</v>
+        <v>252.72</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -882,14 +882,14 @@
         <v>68.11</v>
       </c>
       <c r="I11" t="n">
-        <v>71.8</v>
+        <v>70.02</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>7.16</v>
+        <v>4.51</v>
       </c>
       <c r="L11" t="n">
-        <v>3.69</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="12">
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>78.26000000000001</v>
+        <v>79.03</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>116.9</v>
+        <v>114.32</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1004,14 +1004,14 @@
         <v>52.47</v>
       </c>
       <c r="I14" t="n">
-        <v>52.55</v>
+        <v>51.91</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>0.77</v>
+        <v>-0.46</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>150.03</v>
+        <v>154.03</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>25.08</v>
+        <v>25.02</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>273.61</v>
+        <v>282.83</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>13.64</v>
+        <v>13.4</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>27.81</v>
+        <v>28.35</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>263.45</v>
+        <v>264.73</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>204.1</v>
+        <v>191.72</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>41.65</v>
+        <v>42.07</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1366,14 +1366,14 @@
         <v>67.36</v>
       </c>
       <c r="I23" t="n">
-        <v>33.89</v>
+        <v>33.96</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="L23" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>55.09</v>
+        <v>56.11</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>56.82</v>
+        <v>58.37</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>58.09</v>
+        <v>56.6</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>62.48</v>
+        <v>61.25</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>131.18</v>
+        <v>130.91</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>206.43</v>
+        <v>212.08</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>10.45</v>
+        <v>10.19</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>88.76000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1728,11 +1728,251 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>21.3</v>
+        <v>20.97</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NSIT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>164.73</v>
+      </c>
+      <c r="D33" t="n">
+        <v>160.11</v>
+      </c>
+      <c r="E33" t="n">
+        <v>183.21</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>172.74</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AMG</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="D34" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="E34" t="n">
+        <v>441.35</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PNTG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="D35" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="E35" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ELF</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="D36" t="n">
+        <v>108.29</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-259.36</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>111.69</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>417.18</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-1103.14</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>444.73</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MET</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="D38" t="n">
+        <v>97.17</v>
+      </c>
+      <c r="E38" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
         <v>0</v>
       </c>
     </row>
